--- a/web/public/forms/orig/o-jugan-gongjeong.xlsx
+++ b/web/public/forms/orig/o-jugan-gongjeong.xlsx
@@ -656,7 +656,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="H1" s="28" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="H1" s="28" t="inlineStr">

--- a/web/public/forms/orig/o-jugan-gongjeong.xlsx
+++ b/web/public/forms/orig/o-jugan-gongjeong.xlsx
@@ -9,14 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표지" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추진현황" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-표지" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-추진현황" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'표지'!$A$1:$M$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'추진현황'!$A$1:$M$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'예시-표지'!$A$1:$M$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'예시-추진현황'!$A$1:$M$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -188,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -266,9 +262,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -714,10 +707,7 @@
           <t xml:space="preserve">20       .       .       </t>
         </is>
       </c>
-      <c r="H8" s="8">
-        <f>IF(N(D8)=0,"(      )","("&amp;CHOOSE(WEEKDAY(D8),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
+      <c r="H8" s="8" t="n"/>
       <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="70" customHeight="1"/>
@@ -730,6 +720,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -811,10 +802,7 @@
           <t>▣ 공 사 명 :</t>
         </is>
       </c>
-      <c r="C3" s="13">
-        <f>IF(OR('표지'!C4="",'표지'!C4="공사명"),"",'표지'!C4)</f>
-        <v/>
-      </c>
+      <c r="C3" s="13" t="n"/>
       <c r="D3" s="14" t="n"/>
       <c r="E3" s="14" t="n"/>
       <c r="F3" s="14" t="n"/>
@@ -826,10 +814,7 @@
           <t>회 의 일</t>
         </is>
       </c>
-      <c r="L3" s="16">
-        <f>IF(N('표지'!D8)=0,"",YEAR('표지'!D8)&amp;". "&amp;MONTH('표지'!D8)&amp;". "&amp;DAY('표지'!D8)&amp;". ("&amp;CHOOSE(WEEKDAY('표지'!D8),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
+      <c r="L3" s="16" t="n"/>
       <c r="M3" s="14" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -844,10 +829,7 @@
           <t>금주 시작일(월)</t>
         </is>
       </c>
-      <c r="L4" s="18">
-        <f>IF(N('표지'!D8)=0,"",'표지'!D8-WEEKDAY('표지'!D8,2)+1)</f>
-        <v/>
-      </c>
+      <c r="L4" s="18" t="n"/>
       <c r="M4" s="14" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -934,10 +916,7 @@
       <c r="G7" s="14" t="n"/>
       <c r="H7" s="21" t="n"/>
       <c r="I7" s="14" t="n"/>
-      <c r="J7" s="22">
-        <f>IF(OR(F7="",H7=""),"",ROUND(H7-F7,2))</f>
-        <v/>
-      </c>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="21" t="n"/>
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="23" t="n"/>
@@ -956,19 +935,13 @@
       <c r="G8" s="14" t="n"/>
       <c r="H8" s="21" t="n"/>
       <c r="I8" s="14" t="n"/>
-      <c r="J8" s="22">
-        <f>IF(OR(F8="",H8=""),"",ROUND(H8-F8,2))</f>
-        <v/>
-      </c>
+      <c r="J8" s="22" t="n"/>
       <c r="K8" s="21" t="n"/>
       <c r="L8" s="14" t="n"/>
       <c r="M8" s="14" t="n"/>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="25">
-        <f>IF(N(J7)&lt;0,"⚠ 전체 누계 실적이 계획보다 "&amp;ABS(J7)&amp;"%p 늦습니다 — 만회 대책을 공사추진현황(금주·내주 계획)에 적으세요.","")</f>
-        <v/>
-      </c>
+      <c r="A9" s="25" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -983,24 +956,15 @@
           <t>구  분</t>
         </is>
       </c>
-      <c r="B11" s="26">
-        <f>"전  주"&amp;IF(N(L4)=0,"(   /   ~   /   )","("&amp;MONTH(L4+-7)&amp;"/"&amp;DAY(L4+-7)&amp;" ~ "&amp;MONTH(L4+-1)&amp;"/"&amp;DAY(L4+-1)&amp;")")</f>
-        <v/>
-      </c>
+      <c r="B11" s="26" t="n"/>
       <c r="C11" s="14" t="n"/>
       <c r="D11" s="14" t="n"/>
       <c r="E11" s="14" t="n"/>
-      <c r="F11" s="26">
-        <f>"금  주"&amp;IF(N(L4)=0,"(   /   ~   /   )","("&amp;MONTH(L4+0)&amp;"/"&amp;DAY(L4+0)&amp;" ~ "&amp;MONTH(L4+6)&amp;"/"&amp;DAY(L4+6)&amp;")")</f>
-        <v/>
-      </c>
+      <c r="F11" s="26" t="n"/>
       <c r="G11" s="14" t="n"/>
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="14" t="n"/>
-      <c r="J11" s="26">
-        <f>"내  주"&amp;IF(N(L4)=0,"(   /   ~   /   )","("&amp;MONTH(L4+7)&amp;"/"&amp;DAY(L4+7)&amp;" ~ "&amp;MONTH(L4+13)&amp;"/"&amp;DAY(L4+13)&amp;")")</f>
-        <v/>
-      </c>
+      <c r="J11" s="26" t="n"/>
       <c r="K11" s="14" t="n"/>
       <c r="L11" s="14" t="n"/>
       <c r="M11" s="14" t="n"/>
@@ -1067,6 +1031,7 @@
       <c r="L13" s="14" t="n"/>
       <c r="M13" s="14" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -1132,534 +1097,4 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10.5" customWidth="1" min="2" max="2"/>
-    <col width="10.5" customWidth="1" min="3" max="3"/>
-    <col width="10.5" customWidth="1" min="4" max="4"/>
-    <col width="10.5" customWidth="1" min="5" max="5"/>
-    <col width="10.5" customWidth="1" min="6" max="6"/>
-    <col width="10.5" customWidth="1" min="7" max="7"/>
-    <col width="10.5" customWidth="1" min="8" max="8"/>
-    <col width="10.5" customWidth="1" min="9" max="9"/>
-    <col width="10.5" customWidth="1" min="10" max="10"/>
-    <col width="10.5" customWidth="1" min="11" max="11"/>
-    <col width="10.5" customWidth="1" min="12" max="12"/>
-    <col width="10.5" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="H1" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="66" customHeight="1"/>
-    <row r="3" ht="6" customHeight="1">
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="50" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>주간  공정회의  자료</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="6" customHeight="1">
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="120" customHeight="1"/>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="D8" s="7" t="n">
-        <v>46155</v>
-      </c>
-      <c r="H8" s="8">
-        <f>IF(N(D8)=0,"(      )","("&amp;CHOOSE(WEEKDAY(D8),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="70" customHeight="1"/>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C4:K4"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10.5" customWidth="1" min="2" max="2"/>
-    <col width="10.5" customWidth="1" min="3" max="3"/>
-    <col width="10.5" customWidth="1" min="4" max="4"/>
-    <col width="10.5" customWidth="1" min="5" max="5"/>
-    <col width="10.5" customWidth="1" min="6" max="6"/>
-    <col width="10.5" customWidth="1" min="7" max="7"/>
-    <col width="10.5" customWidth="1" min="8" max="8"/>
-    <col width="10.5" customWidth="1" min="9" max="9"/>
-    <col width="10.5" customWidth="1" min="10" max="10"/>
-    <col width="10.5" customWidth="1" min="11" max="11"/>
-    <col width="10.5" customWidth="1" min="12" max="12"/>
-    <col width="10.5" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="H1" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>주간공정  추진  현황  및  계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>▣ 공 사 명 :</t>
-        </is>
-      </c>
-      <c r="C3" s="13">
-        <f>IF(OR('예시-표지'!C4="",'예시-표지'!C4="공사명"),"",'예시-표지'!C4)</f>
-        <v/>
-      </c>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="14" t="n"/>
-      <c r="G3" s="14" t="n"/>
-      <c r="H3" s="14" t="n"/>
-      <c r="I3" s="14" t="n"/>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>회 의 일</t>
-        </is>
-      </c>
-      <c r="L3" s="16">
-        <f>IF(N('예시-표지'!D8)=0,"",YEAR('예시-표지'!D8)&amp;". "&amp;MONTH('예시-표지'!D8)&amp;". "&amp;DAY('예시-표지'!D8)&amp;". ("&amp;CHOOSE(WEEKDAY('예시-표지'!D8),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
-      <c r="M3" s="14" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>▣ 공 정 율</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t>금주 시작일(월)</t>
-        </is>
-      </c>
-      <c r="L4" s="18">
-        <f>IF(N('예시-표지'!D8)=0,"",'예시-표지'!D8-WEEKDAY('예시-표지'!D8,2)+1)</f>
-        <v/>
-      </c>
-      <c r="M4" s="14" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>구  분</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>전주 실적(%)</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="19" t="inlineStr">
-        <is>
-          <t>전주까지 누계(%)</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="n"/>
-      <c r="I5" s="14" t="n"/>
-      <c r="J5" s="14" t="n"/>
-      <c r="K5" s="19" t="inlineStr">
-        <is>
-          <t>금주계획(%)</t>
-        </is>
-      </c>
-      <c r="L5" s="14" t="n"/>
-      <c r="M5" s="19" t="inlineStr">
-        <is>
-          <t>비  고</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="14" t="n"/>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>계  획</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>실  적</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>계  획</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>실  적</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="n"/>
-      <c r="J6" s="19" t="inlineStr">
-        <is>
-          <t>대  비</t>
-        </is>
-      </c>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>전 체 분</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="21" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="21" t="n">
-        <v>42.85</v>
-      </c>
-      <c r="I7" s="14" t="n"/>
-      <c r="J7" s="22">
-        <f>IF(OR(F7="",H7=""),"",ROUND(H7-F7,2))</f>
-        <v/>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>우천 1일(5/7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>5차분</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="21" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="21" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="I8" s="14" t="n"/>
-      <c r="J8" s="22">
-        <f>IF(OR(F8="",H8=""),"",ROUND(H8-F8,2))</f>
-        <v/>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>78</v>
-      </c>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="14" t="n"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="25">
-        <f>IF(N(J7)&lt;0,"⚠ 전체 누계 실적이 계획보다 "&amp;ABS(J7)&amp;"%p 늦습니다 — 만회 대책을 공사추진현황(금주·내주 계획)에 적으세요.","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>▣ 공사추진현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>구  분</t>
-        </is>
-      </c>
-      <c r="B11" s="26">
-        <f>"전  주"&amp;IF(N(L4)=0,"(   /   ~   /   )","("&amp;MONTH(L4+-7)&amp;"/"&amp;DAY(L4+-7)&amp;" ~ "&amp;MONTH(L4+-1)&amp;"/"&amp;DAY(L4+-1)&amp;")")</f>
-        <v/>
-      </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="26">
-        <f>"금  주"&amp;IF(N(L4)=0,"(   /   ~   /   )","("&amp;MONTH(L4+0)&amp;"/"&amp;DAY(L4+0)&amp;" ~ "&amp;MONTH(L4+6)&amp;"/"&amp;DAY(L4+6)&amp;")")</f>
-        <v/>
-      </c>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="n"/>
-      <c r="I11" s="14" t="n"/>
-      <c r="J11" s="26">
-        <f>"내  주"&amp;IF(N(L4)=0,"(   /   ~   /   )","("&amp;MONTH(L4+7)&amp;"/"&amp;DAY(L4+7)&amp;" ~ "&amp;MONTH(L4+13)&amp;"/"&amp;DAY(L4+13)&amp;")")</f>
-        <v/>
-      </c>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>계  획</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>○ 배수로 터파기 STA.0+120 ~ 0+200
-○ PC 암거 거치 12개
-○ 되메우기 L=60m</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="27" t="inlineStr">
-        <is>
-          <t>○ 터파기 STA.0+180 ~ 0+260
-○ PC 암거 거치 14개(전주 잔여 2개 포함)
-○ 되메우기 L=80m</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
-      <c r="I12" s="14" t="n"/>
-      <c r="J12" s="27" t="inlineStr">
-        <is>
-          <t>○ 터파기 STA.0+260 ~ 0+340
-○ PC 암거 거치 12개
-○ 보도블록 포장 자재 반입</t>
-        </is>
-      </c>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-    </row>
-    <row r="13" ht="112" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>실  적</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>○ 배수로 터파기 STA.0+120 ~ 0+180 (우천 1일)
-○ PC 암거 거치 10개
-○ 되메우기 L=45m</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="27" t="inlineStr">
-        <is>
-          <t>○ 터파기 STA.0+180 ~ 0+220 (5/11 ~ 5/12)
-○ PC 암거 거치 6개</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="14" t="n"/>
-      <c r="I13" s="14" t="n"/>
-      <c r="J13" s="27" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="14" t="n"/>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="K5:L6"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="M5:M6"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/orig/o-jugan-gongjeong.xlsx
+++ b/web/public/forms/orig/o-jugan-gongjeong.xlsx
@@ -649,7 +649,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
